--- a/docs/assets/documents/ref/StructureDefinition-patient.xlsx
+++ b/docs/assets/documents/ref/StructureDefinition-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T14:56:57+02:00</t>
+    <t>2026-06-25T17:09:01+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
